--- a/sources/kuma_step4.xlsx
+++ b/sources/kuma_step4.xlsx
@@ -738,6 +738,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>c22a7071-9fc0-4903-b56c-1f6dfac34d0c</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>c22a7071-9fc0-4903-b56c-1f6dfac34d0c</t>
@@ -780,6 +785,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6dbc1aef-8267-41ba-b27b-7d3a9e2d9f70</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>6dbc1aef-8267-41ba-b27b-7d3a9e2d9f70</t>
@@ -822,6 +832,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4138c35c-823c-4c4c-ab33-0edf2448c1bd</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>4138c35c-823c-4c4c-ab33-0edf2448c1bd</t>
@@ -862,6 +877,11 @@
       <c r="L10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>d84f5821-e8c2-4b13-80d7-7f78bb38c6d1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">

--- a/sources/kuma_step4.xlsx
+++ b/sources/kuma_step4.xlsx
@@ -4330,6 +4330,11 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>– Sitting Claws</t>
@@ -4417,6 +4422,11 @@
       <c r="A81" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
